--- a/Assignments/Excel_Logical_Functions_assignment.xlsx
+++ b/Assignments/Excel_Logical_Functions_assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f5269e412419e72/Documents/Excel ITvedant/Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{1D3CE1E0-F970-456F-8A5F-B1CCAD79CD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F45DEA6C-43F6-42F3-9D15-FCC6E261B270}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{1D3CE1E0-F970-456F-8A5F-B1CCAD79CD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3754BD8B-EA4C-4497-8843-2202D0929410}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Employee Dataset" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <definedName name="Salary">'🔢 Nested IF &amp; IFS'!$C$4:$C$28</definedName>
     <definedName name="Status">'⚡ AND, OR, NOT'!$E$4:$E$28</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1919,6 +1919,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1943,10 +1947,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2311,20 +2311,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -2401,7 +2401,7 @@
       <c r="L3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="57"/>
+      <c r="N3" s="49"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
@@ -2478,7 +2478,7 @@
       <c r="L5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="57"/>
+      <c r="N5" s="49"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
@@ -3344,14 +3344,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -3721,28 +3721,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -4545,28 +4545,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -5412,26 +5412,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -6137,28 +6137,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -6990,48 +6990,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="53" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -7207,65 +7207,65 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="50">
+      <c r="B12" s="52">
         <f>COUNTIF('📋 Employee Dataset'!B3:B27,"A*")</f>
         <v>1</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
     </row>
     <row r="13" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="50">
+      <c r="B13" s="52">
         <f>COUNTIF('📋 Employee Dataset'!E3:E27,"&gt;80000")</f>
         <v>6</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
     </row>
     <row r="14" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="50">
+      <c r="B14" s="52">
         <f>SUMIFS('📋 Employee Dataset'!E3:E27,'📋 Employee Dataset'!E3:E27,"&gt;=60000",'📋 Employee Dataset'!E3:E27,"&lt;=80000")</f>
         <v>1106000</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -7297,37 +7297,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -7498,28 +7498,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -8366,20 +8366,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -8396,7 +8396,7 @@
       <c r="B5" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="48" t="s">
         <v>301</v>
       </c>
       <c r="D5" s="19" t="s">
@@ -8410,7 +8410,7 @@
       <c r="B6" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="48" t="s">
         <v>302</v>
       </c>
       <c r="D6" s="19" t="s">
@@ -8432,7 +8432,7 @@
       <c r="B8" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="48" t="s">
         <v>303</v>
       </c>
       <c r="D8" s="21" t="s">
@@ -8454,7 +8454,7 @@
       <c r="B10" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="48" t="s">
         <v>304</v>
       </c>
       <c r="D10" s="21" t="s">
@@ -8476,7 +8476,7 @@
       <c r="B12" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="48" t="s">
         <v>305</v>
       </c>
       <c r="D12" s="21" t="s">
@@ -8498,7 +8498,7 @@
       <c r="B14" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="48" t="s">
         <v>306</v>
       </c>
       <c r="D14" s="21" t="s">
@@ -8520,7 +8520,7 @@
       <c r="B16" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="48" t="s">
         <v>307</v>
       </c>
       <c r="D16" s="21" t="s">
@@ -8542,7 +8542,7 @@
       <c r="B18" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="48" t="s">
         <v>308</v>
       </c>
       <c r="D18" s="19" t="s">
@@ -8564,7 +8564,7 @@
       <c r="B20" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="48" t="s">
         <v>309</v>
       </c>
       <c r="D20" s="19" t="s">
@@ -8586,7 +8586,7 @@
       <c r="B22" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="48" t="s">
         <v>310</v>
       </c>
       <c r="D22" s="21" t="s">
@@ -8608,7 +8608,7 @@
       <c r="B24" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="48" t="s">
         <v>315</v>
       </c>
       <c r="D24" s="22" t="s">
@@ -8630,7 +8630,7 @@
       <c r="B26" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="56" t="s">
+      <c r="C26" s="48" t="s">
         <v>311</v>
       </c>
       <c r="D26" s="22" t="s">
@@ -8652,7 +8652,7 @@
       <c r="B28" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="48" t="s">
         <v>312</v>
       </c>
       <c r="D28" s="21" t="s">
@@ -8674,7 +8674,7 @@
       <c r="B30" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="48" t="s">
         <v>313</v>
       </c>
       <c r="D30" s="21" t="s">
@@ -8696,7 +8696,7 @@
       <c r="B32" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="48" t="s">
         <v>314</v>
       </c>
       <c r="D32" s="22" t="s">
